--- a/lista_reporte_de_multas_sector_b.xlsx
+++ b/lista_reporte_de_multas_sector_b.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maric\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maric\Desktop\auto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48FFFF40-ACA0-483B-8CDA-77777B5CC33F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A210D755-4524-422D-94B5-68C413163E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="83">
   <si>
     <t>NOMBRE</t>
   </si>
@@ -278,13 +278,25 @@
   </si>
   <si>
     <t xml:space="preserve">aun falta </t>
+  </si>
+  <si>
+    <t>1 EIRL ADVANCED LOGISTICS GROUP (ALG) 20511032114 ADVANC55 ShalomJireh6</t>
+  </si>
+  <si>
+    <t>EIRL ADVANCED LOGISTICS GROUP (ALG)</t>
+  </si>
+  <si>
+    <t>ADVANC55</t>
+  </si>
+  <si>
+    <t>ShalomJireh6</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -334,6 +346,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -395,7 +413,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -461,6 +479,10 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1011,6 +1033,21 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="3">
+        <v>20511032114</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>82</v>
+      </c>
       <c r="G14"/>
       <c r="H14"/>
       <c r="I14"/>
@@ -1236,7 +1273,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21D48956-9A91-4972-87C7-1A65D5E09CD0}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="11.44140625" style="23"/>
@@ -1427,6 +1464,11 @@
         <v>78</v>
       </c>
     </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="25" t="s">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/lista_reporte_de_multas_sector_b.xlsx
+++ b/lista_reporte_de_multas_sector_b.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maric\Desktop\auto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A210D755-4524-422D-94B5-68C413163E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E90955-1319-4BA8-B4A2-95B71882C851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2988" yWindow="2100" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA" sheetId="1" r:id="rId1"/>
@@ -283,13 +283,13 @@
     <t>1 EIRL ADVANCED LOGISTICS GROUP (ALG) 20511032114 ADVANC55 ShalomJireh6</t>
   </si>
   <si>
-    <t>EIRL ADVANCED LOGISTICS GROUP (ALG)</t>
-  </si>
-  <si>
-    <t>ADVANC55</t>
-  </si>
-  <si>
-    <t>ShalomJireh6</t>
+    <t>IFTERATC</t>
+  </si>
+  <si>
+    <t>omogonjug</t>
+  </si>
+  <si>
+    <t>GLOVAL SHIPPING LATIN AMERICA (PERU) S.R.L</t>
   </si>
 </sst>
 </file>
@@ -480,8 +480,8 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1033,20 +1033,20 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
+      <c r="A14" s="26">
         <v>13</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" s="3">
+        <v>20603083050</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="3">
-        <v>20511032114</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="E14" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>82</v>
       </c>
       <c r="G14"/>
       <c r="H14"/>

--- a/lista_reporte_de_multas_sector_b.xlsx
+++ b/lista_reporte_de_multas_sector_b.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maric\Desktop\auto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E90955-1319-4BA8-B4A2-95B71882C851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FAC318E-85EB-485D-9A34-5DCD4C3CEAEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2988" yWindow="2100" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="82">
   <si>
     <t>NOMBRE</t>
   </si>
@@ -283,20 +283,17 @@
     <t>1 EIRL ADVANCED LOGISTICS GROUP (ALG) 20511032114 ADVANC55 ShalomJireh6</t>
   </si>
   <si>
-    <t>IFTERATC</t>
-  </si>
-  <si>
-    <t>omogonjug</t>
-  </si>
-  <si>
-    <t>GLOVAL SHIPPING LATIN AMERICA (PERU) S.R.L</t>
+    <t>SCHRYVER</t>
+  </si>
+  <si>
+    <t>2024D4rils</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -353,8 +350,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -376,12 +379,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -413,7 +410,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,11 +475,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -763,7 +756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.5546875" style="2" customWidth="1"/>
@@ -796,7 +789,7 @@
       <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C2" s="3">
@@ -1033,14 +1026,14 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="26">
+      <c r="A14" s="3">
         <v>13</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C14" s="3">
-        <v>20603083050</v>
+        <v>20545207436</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>80</v>
@@ -1048,6 +1041,7 @@
       <c r="E14" s="4" t="s">
         <v>81</v>
       </c>
+      <c r="F14"/>
       <c r="G14"/>
       <c r="H14"/>
       <c r="I14"/>
@@ -1114,19 +1108,8 @@
       <c r="J19"/>
       <c r="K19"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20"/>
-      <c r="F20"/>
-      <c r="G20"/>
-      <c r="H20"/>
-      <c r="I20"/>
-      <c r="J20"/>
-      <c r="K20"/>
-    </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
@@ -1465,7 +1448,7 @@
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="25" t="s">
+      <c r="A18" s="24" t="s">
         <v>79</v>
       </c>
     </row>

--- a/lista_reporte_de_multas_sector_b.xlsx
+++ b/lista_reporte_de_multas_sector_b.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maric\Desktop\auto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FAC318E-85EB-485D-9A34-5DCD4C3CEAEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5B3E7E-3E7C-4121-9E15-F24A88EE62AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="80">
   <si>
     <t>NOMBRE</t>
   </si>
@@ -281,12 +281,6 @@
   </si>
   <si>
     <t>1 EIRL ADVANCED LOGISTICS GROUP (ALG) 20511032114 ADVANC55 ShalomJireh6</t>
-  </si>
-  <si>
-    <t>SCHRYVER</t>
-  </si>
-  <si>
-    <t>2024D4rils</t>
   </si>
 </sst>
 </file>
@@ -756,7 +750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.5546875" style="2" customWidth="1"/>
@@ -1026,21 +1020,10 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
-        <v>13</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="C14" s="3">
-        <v>20545207436</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>81</v>
-      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14"/>
       <c r="F14"/>
       <c r="G14"/>
       <c r="H14"/>
@@ -1095,18 +1078,6 @@
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19"/>
-      <c r="F19"/>
-      <c r="G19"/>
-      <c r="H19"/>
-      <c r="I19"/>
-      <c r="J19"/>
-      <c r="K19"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>

--- a/lista_reporte_de_multas_sector_b.xlsx
+++ b/lista_reporte_de_multas_sector_b.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maric\Desktop\auto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5B3E7E-3E7C-4121-9E15-F24A88EE62AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ABB558D-8AA5-44AC-8870-5F127ED22EDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA" sheetId="1" r:id="rId1"/>
@@ -404,7 +404,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -452,7 +452,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -470,6 +469,11 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -803,16 +807,16 @@
       <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="25">
         <v>20604081964</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="26" t="s">
         <v>32</v>
       </c>
       <c r="F3" s="2" t="s">
@@ -1015,7 +1019,7 @@
       <c r="E13" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F13" s="17" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1230,30 +1234,30 @@
   <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.44140625" style="23"/>
+    <col min="1" max="2" width="11.44140625" style="22"/>
     <col min="3" max="3" width="45.88671875" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="19"/>
+    <col min="4" max="4" width="11.44140625" style="18"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="20" t="s">
         <v>64</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="19" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="21" t="s">
         <v>65</v>
       </c>
       <c r="C2" s="14" t="s">
@@ -1264,10 +1268,10 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="14" t="s">
@@ -1278,10 +1282,10 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="21" t="s">
         <v>65</v>
       </c>
       <c r="C4" s="14" t="s">
@@ -1292,10 +1296,10 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>65</v>
       </c>
       <c r="C5" s="14" t="s">
@@ -1306,10 +1310,10 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>65</v>
       </c>
       <c r="C6" s="14" t="s">
@@ -1320,10 +1324,10 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>77</v>
       </c>
       <c r="C7" s="14" t="s">
@@ -1334,10 +1338,10 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>65</v>
       </c>
       <c r="C8" s="14" t="s">
@@ -1348,10 +1352,10 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="21" t="s">
         <v>65</v>
       </c>
       <c r="C9" s="14" t="s">
@@ -1362,10 +1366,10 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="21" t="s">
         <v>65</v>
       </c>
       <c r="C10" s="14" t="s">
@@ -1376,10 +1380,10 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="21" t="s">
         <v>65</v>
       </c>
       <c r="C11" s="14" t="s">
@@ -1390,10 +1394,10 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="21" t="s">
         <v>65</v>
       </c>
       <c r="C12" s="14" t="s">
@@ -1404,10 +1408,10 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="21" t="s">
         <v>65</v>
       </c>
       <c r="C13" s="14" t="s">
@@ -1419,7 +1423,7 @@
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="23" t="s">
         <v>79</v>
       </c>
     </row>
